--- a/3 Bug Reports/Bug Reports.xlsx
+++ b/3 Bug Reports/Bug Reports.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\Project 1- On manual testing\3 Bug Reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\Manual-Testing---OrangeHRM-Demo-Website-\3 Bug Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDFD2C3B-2327-4515-BEA1-4F46A4A3B93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B08959DA-E3F9-4C43-B794-5F6776534A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -291,9 +291,6 @@
     <t>Employee Id: 1238abcde</t>
   </si>
   <si>
-    <t>Google Chrome</t>
-  </si>
-  <si>
     <t>TC_43</t>
   </si>
   <si>
@@ -673,6 +670,10 @@
   </si>
   <si>
     <t>Driver's License Number field accepts special character</t>
+  </si>
+  <si>
+    <t>Windows 11, 
+Google Chrome</t>
   </si>
 </sst>
 </file>
@@ -746,7 +747,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -790,9 +791,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -802,7 +800,56 @@
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.14996795556505021"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -813,220 +860,9 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="9" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.14996795556505021"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1071,6 +907,14 @@
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -1107,35 +951,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}" name="Table2" displayName="Table2" ref="A1:B7" totalsRowShown="0" headerRowDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}" name="Table2" displayName="Table2" ref="A1:B7" totalsRowShown="0" headerRowDxfId="28">
   <autoFilter ref="A1:B7" xr:uid="{E7067C6F-9DB2-4A57-AB11-D11197847C24}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{CCDBE3D5-BA30-452E-909C-7F873D8A70DA}" name="Name" dataDxfId="49"/>
-    <tableColumn id="2" xr3:uid="{A5779E73-DBC0-465F-900A-DD37322B0CB2}" name="Information" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{CCDBE3D5-BA30-452E-909C-7F873D8A70DA}" name="Name" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{A5779E73-DBC0-465F-900A-DD37322B0CB2}" name="Information" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}" name="Table3" displayName="Table3" ref="A9:O32" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}" name="Table3" displayName="Table3" ref="A9:O32" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24">
   <autoFilter ref="A9:O32" xr:uid="{D8332838-4407-4B34-BB3C-DB98A0EC423F}"/>
   <tableColumns count="15">
-    <tableColumn id="13" xr3:uid="{E4B65E3A-8DC6-4A74-99EE-23D66BD198AE}" name="Bug ID" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{CF81CC45-2196-4B2D-B752-C5CE3993D436}" name="Bug Title" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{79DE2349-3CBC-4143-8CC4-2A916E332E1A}" name="Test Case ID" dataDxfId="45"/>
-    <tableColumn id="1" xr3:uid="{84819441-F443-4D12-9CA1-9068D48C8291}" name="Module" dataDxfId="44" dataCellStyle="Currency"/>
-    <tableColumn id="5" xr3:uid="{EA95E4DF-21F9-4B1B-B053-F3C10576A572}" name="Preconditions" dataDxfId="43" dataCellStyle="Normal"/>
-    <tableColumn id="6" xr3:uid="{C41CB108-4FDE-48FA-A32A-530EC33A9B95}" name="Steps" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{76C9D7D3-DEF7-446D-98B7-1E0A8B648542}" name="Test Data" dataDxfId="41"/>
-    <tableColumn id="17" xr3:uid="{AB0270D7-8FB5-43C0-BFC2-362BB1C6DB6A}" name="Priority" dataDxfId="40"/>
-    <tableColumn id="16" xr3:uid="{ABB40573-C686-422F-AF00-46C25CEC899A}" name="Severity" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{CCCFA774-F91F-4816-BA60-27DE55A487FF}" name="Expected Result" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{71D61FE6-98A2-4210-837C-F2BBF530F9E5}" name="Actual Result" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{AB495624-3700-40F0-9D3F-4A48458D2841}" name="Testing environment" dataDxfId="36"/>
-    <tableColumn id="10" xr3:uid="{1C2CA1F8-A497-48AD-8741-469AE5F239CA}" name="Status" dataDxfId="35"/>
-    <tableColumn id="11" xr3:uid="{0BA41AF9-03FC-4396-BE33-D5B87DA0A07D}" name="Attachment " dataDxfId="34"/>
-    <tableColumn id="12" xr3:uid="{42278E2B-9A99-4E11-A447-FD44432F578F}" name="Comments / Notes" dataDxfId="33"/>
+    <tableColumn id="13" xr3:uid="{E4B65E3A-8DC6-4A74-99EE-23D66BD198AE}" name="Bug ID" dataDxfId="23"/>
+    <tableColumn id="14" xr3:uid="{CF81CC45-2196-4B2D-B752-C5CE3993D436}" name="Bug Title" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{79DE2349-3CBC-4143-8CC4-2A916E332E1A}" name="Test Case ID" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{84819441-F443-4D12-9CA1-9068D48C8291}" name="Module" dataDxfId="20" dataCellStyle="Currency"/>
+    <tableColumn id="5" xr3:uid="{EA95E4DF-21F9-4B1B-B053-F3C10576A572}" name="Preconditions" dataDxfId="19" dataCellStyle="Normal"/>
+    <tableColumn id="6" xr3:uid="{C41CB108-4FDE-48FA-A32A-530EC33A9B95}" name="Steps" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{76C9D7D3-DEF7-446D-98B7-1E0A8B648542}" name="Test Data" dataDxfId="17"/>
+    <tableColumn id="17" xr3:uid="{AB0270D7-8FB5-43C0-BFC2-362BB1C6DB6A}" name="Priority" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{ABB40573-C686-422F-AF00-46C25CEC899A}" name="Severity" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{CCCFA774-F91F-4816-BA60-27DE55A487FF}" name="Expected Result" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{71D61FE6-98A2-4210-837C-F2BBF530F9E5}" name="Actual Result" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{AB495624-3700-40F0-9D3F-4A48458D2841}" name="Testing environment" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{1C2CA1F8-A497-48AD-8741-469AE5F239CA}" name="Status" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{0BA41AF9-03FC-4396-BE33-D5B87DA0A07D}" name="Attachment " dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{42278E2B-9A99-4E11-A447-FD44432F578F}" name="Comments / Notes" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium25" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1438,7 +1282,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
@@ -1482,11 +1326,11 @@
       <c r="B7" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>144</v>
+      <c r="A9" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>10</v>
@@ -1530,10 +1374,10 @@
     </row>
     <row r="10" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>28</v>
@@ -1555,28 +1399,28 @@
         <v>24</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>29</v>
@@ -1598,28 +1442,28 @@
         <v>24</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>30</v>
@@ -1641,28 +1485,28 @@
         <v>24</v>
       </c>
       <c r="J12" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N12" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>31</v>
@@ -1684,28 +1528,28 @@
         <v>24</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>37</v>
@@ -1727,28 +1571,28 @@
         <v>24</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N14" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>38</v>
@@ -1770,28 +1614,28 @@
         <v>24</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N15" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>39</v>
@@ -1813,29 +1657,29 @@
         <v>24</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
     <row r="17" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>41</v>
@@ -1857,29 +1701,29 @@
         <v>24</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N17" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>51</v>
@@ -1901,29 +1745,29 @@
         <v>24</v>
       </c>
       <c r="J18" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M18" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N18" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
     <row r="19" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>52</v>
@@ -1945,29 +1789,29 @@
         <v>24</v>
       </c>
       <c r="J19" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N19" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
     </row>
     <row r="20" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>53</v>
@@ -1989,29 +1833,29 @@
         <v>24</v>
       </c>
       <c r="J20" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N20" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
     </row>
     <row r="21" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>54</v>
@@ -2033,29 +1877,29 @@
         <v>24</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N21" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
     </row>
     <row r="22" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>55</v>
@@ -2077,29 +1921,29 @@
         <v>24</v>
       </c>
       <c r="J22" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K22" s="6" t="s">
         <v>46</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
     </row>
     <row r="23" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>69</v>
@@ -2121,29 +1965,29 @@
         <v>24</v>
       </c>
       <c r="J23" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K23" s="6" t="s">
         <v>46</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N23" s="14" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O23" s="6"/>
       <c r="P23" s="6"/>
     </row>
     <row r="24" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>70</v>
@@ -2165,130 +2009,130 @@
         <v>24</v>
       </c>
       <c r="J24" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K24" s="6" t="s">
         <v>46</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M24" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
     </row>
     <row r="25" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="11"/>
       <c r="E25" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F25" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="H25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="H25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="L25" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N25" s="14" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
     </row>
     <row r="26" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J26" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="K26" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
     </row>
     <row r="27" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D27" s="9"/>
       <c r="E27" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>24</v>
@@ -2297,86 +2141,86 @@
         <v>24</v>
       </c>
       <c r="J27" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M27" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N27" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
     </row>
     <row r="28" spans="1:16" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="J28" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>104</v>
-      </c>
       <c r="K28" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M28" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
     </row>
     <row r="29" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>23</v>
@@ -2385,42 +2229,42 @@
         <v>24</v>
       </c>
       <c r="J29" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M29" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N29" s="14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O29" s="6"/>
       <c r="P29" s="6"/>
     </row>
     <row r="30" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D30" s="9"/>
       <c r="E30" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>111</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>23</v>
@@ -2429,42 +2273,42 @@
         <v>24</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M30" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N30" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
     </row>
     <row r="31" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D31" s="9"/>
       <c r="E31" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F31" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>113</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>23</v>
@@ -2473,42 +2317,42 @@
         <v>24</v>
       </c>
       <c r="J31" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M31" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N31" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="O31" s="16"/>
+        <v>137</v>
+      </c>
+      <c r="O31" s="15"/>
       <c r="P31" s="6"/>
     </row>
     <row r="32" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D32" s="7"/>
       <c r="E32" s="6" t="s">
         <v>22</v>
       </c>
       <c r="F32" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>114</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>115</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>23</v>
@@ -2517,19 +2361,19 @@
         <v>24</v>
       </c>
       <c r="J32" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="M32" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="N32" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O32" s="6"/>
       <c r="P32" s="6"/>
@@ -2567,32 +2411,32 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="M10:M32">
-    <cfRule type="cellIs" dxfId="9" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+      <formula>"Fixed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+      <formula>"Open"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
+      <formula>"New"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="7" operator="equal">
       <formula>"N/A"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"Passed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
-      <formula>"New"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
-      <formula>"Open"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"Fixed"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
